--- a/Noir Wingman/Assets/Sheets/Demo Dialogue/WillyGoldberg/WillGoldbern_0.1.xlsx
+++ b/Noir Wingman/Assets/Sheets/Demo Dialogue/WillyGoldberg/WillGoldbern_0.1.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\coles\OneDrive\Desktop\NoirWingman\Noir Wingman\Assets\Sheets\Demo Dialogue\WillyGoldberg\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b685ca5cabcdd482/Desktop/NoirWingman/Noir Wingman/Assets/Sheets/Demo Dialogue/WillyGoldberg/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02D2D6C6-784E-4BDA-B5E7-DCB0A9DEE23B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>

--- a/Noir Wingman/Assets/Sheets/Demo Dialogue/WillyGoldberg/WillGoldbern_0.1.xlsx
+++ b/Noir Wingman/Assets/Sheets/Demo Dialogue/WillyGoldberg/WillGoldbern_0.1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b685ca5cabcdd482/Desktop/NoirWingman/Noir Wingman/Assets/Sheets/Demo Dialogue/WillyGoldberg/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02D2D6C6-784E-4BDA-B5E7-DCB0A9DEE23B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{02D2D6C6-784E-4BDA-B5E7-DCB0A9DEE23B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2E2A86B-748D-43F5-94BF-0490FB80C64D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15620" xr2:uid="{86F17A0F-ED87-4479-9A3A-D6E930E112F9}"/>
   </bookViews>
@@ -167,9 +167,6 @@
     <t>Neutral|Neutral|Sad|Sad</t>
   </si>
   <si>
-    <t>3|3|0|4</t>
-  </si>
-  <si>
     <t>Willy Goldbern|Willy Goldbern| Detective Juels|Willy Goldbern</t>
   </si>
   <si>
@@ -179,9 +176,6 @@
     <t>Angry|Neutral</t>
   </si>
   <si>
-    <t>4|4</t>
-  </si>
-  <si>
     <t xml:space="preserve">Willy Goldbern|Willy Goldbern </t>
   </si>
   <si>
@@ -276,6 +270,12 @@
   </si>
   <si>
     <t>2|3|0|3|0</t>
+  </si>
+  <si>
+    <t>3|3|0|3</t>
+  </si>
+  <si>
+    <t>3|3</t>
   </si>
 </sst>
 </file>
@@ -862,19 +862,19 @@
         <v>2</v>
       </c>
       <c r="H5" t="s">
+        <v>54</v>
+      </c>
+      <c r="I5" t="s">
+        <v>55</v>
+      </c>
+      <c r="J5" t="s">
         <v>56</v>
       </c>
-      <c r="I5" t="s">
-        <v>57</v>
-      </c>
-      <c r="J5" t="s">
-        <v>58</v>
-      </c>
       <c r="K5" t="s">
+        <v>77</v>
+      </c>
+      <c r="L5" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>43</v>
       </c>
       <c r="M5">
         <v>0</v>
@@ -891,10 +891,10 @@
         <v>35</v>
       </c>
       <c r="C6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" t="s">
         <v>44</v>
-      </c>
-      <c r="D6" t="s">
-        <v>45</v>
       </c>
       <c r="E6" t="s">
         <v>36</v>
@@ -915,10 +915,10 @@
         <v>1</v>
       </c>
       <c r="K6" t="s">
-        <v>46</v>
+        <v>78</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="M6">
         <v>0</v>
@@ -929,16 +929,16 @@
     </row>
     <row r="7" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="B7" t="s">
+      <c r="D7" t="s">
         <v>48</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="D7" t="s">
-        <v>50</v>
       </c>
       <c r="E7" t="s">
         <v>36</v>
@@ -959,10 +959,10 @@
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="M7">
         <v>0</v>
@@ -973,16 +973,16 @@
     </row>
     <row r="8" spans="1:14" ht="72.5" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
+        <v>51</v>
+      </c>
+      <c r="B8" t="s">
+        <v>61</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D8" t="s">
         <v>53</v>
-      </c>
-      <c r="B8" t="s">
-        <v>63</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D8" t="s">
-        <v>55</v>
       </c>
       <c r="E8" t="s">
         <v>38</v>
@@ -1003,10 +1003,10 @@
         <v>1</v>
       </c>
       <c r="K8" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="M8">
         <v>0</v>
@@ -1017,16 +1017,16 @@
     </row>
     <row r="9" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="E9" t="s">
         <v>38</v>
@@ -1047,10 +1047,10 @@
         <v>1</v>
       </c>
       <c r="K9" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L9" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M9">
         <v>0</v>
@@ -1061,16 +1061,16 @@
     </row>
     <row r="10" spans="1:14" ht="29" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
+        <v>66</v>
+      </c>
+      <c r="B10" t="s">
+        <v>67</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B10" t="s">
+      <c r="D10" t="s">
         <v>69</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="D10" t="s">
-        <v>71</v>
       </c>
       <c r="E10" t="s">
         <v>38</v>
@@ -1091,10 +1091,10 @@
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="M10">
         <v>0</v>
@@ -1105,16 +1105,16 @@
     </row>
     <row r="11" spans="1:14" ht="130.5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" t="s">
+        <v>71</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="B11" t="s">
+      <c r="D11" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="E11" t="s">
         <v>38</v>
@@ -1135,10 +1135,10 @@
         <v>0</v>
       </c>
       <c r="K11" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="M11">
         <v>0</v>
